--- a/web/files/九龙-西九龙站-天玺.xlsx
+++ b/web/files/九龙-西九龙站-天玺.xlsx
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1775</v>
+        <v>1798</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>231968000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>130686</v>
+        <v>129014</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>231968000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>130686</v>
+        <v>129014</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -52389,9 +52389,9 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>C | 1775呎 (4+房)
+          <t>C | 1798呎 (4+房)
 $23197万
-$130,686/呎
+$129,014/呎
 (25年-08月-26日)</t>
         </is>
       </c>

--- a/web/files/九龙-西九龙站-天玺.xlsx
+++ b/web/files/九龙-西九龙站-天玺.xlsx
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>20662200</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>30839</v>
+        <v>30565</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>20662200</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>30839</v>
+        <v>30565</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
@@ -54350,9 +54350,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 670呎 (2房)
+          <t>E | 676呎 (2房)
 $2066万
-$30,839/呎
+$30,565/呎
 (12年-04月-18日)</t>
         </is>
       </c>
